--- a/artfynd/A 17341-2025 artfynd.xlsx
+++ b/artfynd/A 17341-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105372663</v>
+        <v>105372645</v>
       </c>
       <c r="B2" t="n">
-        <v>8367</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689473.7818951077</v>
+        <v>689499</v>
       </c>
       <c r="R2" t="n">
-        <v>6609447.865225326</v>
+        <v>6609516</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -792,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105372645</v>
+        <v>105372663</v>
       </c>
       <c r="B3" t="n">
-        <v>8367</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689498.7940580926</v>
+        <v>689474</v>
       </c>
       <c r="R3" t="n">
-        <v>6609516.104673556</v>
+        <v>6609447</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
